--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_2_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_2_branch.xlsx
@@ -646,16 +646,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.282962610066684</v>
+        <v>4.282962610066685</v>
       </c>
       <c r="C2">
-        <v>4.282962610066684</v>
+        <v>4.282962610066685</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.277811204449897</v>
+        <v>9.277811204449899</v>
       </c>
       <c r="F2">
         <v>148.3661769510661</v>
@@ -664,31 +664,31 @@
         <v>148.3661769510661</v>
       </c>
       <c r="H2">
-        <v>28.61627979050449</v>
+        <v>28.61627979050433</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>32.46847082824988</v>
+        <v>32.46847082824983</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-77.77984579421404</v>
+        <v>-77.77984579421408</v>
       </c>
       <c r="M2">
-        <v>102.2201542057787</v>
+        <v>102.2201542057786</v>
       </c>
       <c r="N2">
-        <v>0.291705603738297</v>
+        <v>0.2917056037382958</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-29.17137735526047</v>
+        <v>-29.17137735526041</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.709154423744986</v>
+        <v>3.709154423744984</v>
       </c>
       <c r="D2">
-        <v>3.70915442374498</v>
+        <v>3.709154423744984</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -855,16 +855,16 @@
         <v>3.709154423744982</v>
       </c>
       <c r="G2">
-        <v>3.70915442374498</v>
+        <v>3.709154423744983</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42.82962610030117</v>
+        <v>42.82962610030116</v>
       </c>
       <c r="J2">
-        <v>42.82962610030111</v>
+        <v>42.82962610030116</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -873,43 +873,43 @@
         <v>42.82962610030114</v>
       </c>
       <c r="M2">
-        <v>42.82962610030111</v>
+        <v>42.82962610030115</v>
       </c>
       <c r="N2">
-        <v>5.210646841809276E-15</v>
+        <v>-2.084258736723716E-14</v>
       </c>
       <c r="O2">
-        <v>30.17661447772225</v>
+        <v>30.17661447772224</v>
       </c>
       <c r="P2">
-        <v>-15.86847458187514</v>
+        <v>-15.86847458187515</v>
       </c>
       <c r="Q2">
-        <v>-1.042129368361845E-14</v>
+        <v>1.042129368361855E-14</v>
       </c>
       <c r="R2">
-        <v>-23.02254452973952</v>
+        <v>-23.02254452973953</v>
       </c>
       <c r="S2">
-        <v>23.02254452985796</v>
+        <v>23.02254452985798</v>
       </c>
       <c r="T2">
-        <v>5.048801407653465E-29</v>
+        <v>5.210646841809074E-15</v>
       </c>
       <c r="U2">
-        <v>3.130989834187413</v>
+        <v>3.130989834187383</v>
       </c>
       <c r="V2">
-        <v>13.10324558045217</v>
+        <v>13.10324558045218</v>
       </c>
       <c r="W2">
-        <v>-1.042129368361866E-14</v>
+        <v>1.021911946759858E-28</v>
       </c>
       <c r="X2">
-        <v>4.98612787313473</v>
+        <v>4.986127873134759</v>
       </c>
       <c r="Y2">
-        <v>-4.986127873130088</v>
+        <v>-4.986127873130076</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -918,13 +918,13 @@
         <v>-167.7798457937528</v>
       </c>
       <c r="AB2">
-        <v>12.22015420623989</v>
+        <v>12.22015420623993</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>12.2201542062399</v>
+        <v>12.22015420623994</v>
       </c>
       <c r="AE2">
         <v>-167.7798457937528</v>
@@ -933,22 +933,22 @@
         <v>1.10000002383429</v>
       </c>
       <c r="AG2">
-        <v>0.7083556674758256</v>
+        <v>0.7083556674758258</v>
       </c>
       <c r="AH2">
-        <v>0.4804898682203932</v>
+        <v>0.4804898682203931</v>
       </c>
       <c r="AI2">
         <v>1.10000002383429</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119158037</v>
+        <v>0.5500000119158042</v>
       </c>
       <c r="AK2">
         <v>0.5500000119184837</v>
       </c>
       <c r="AL2">
-        <v>5.551614243689499E-13</v>
+        <v>5.561273881826139E-13</v>
       </c>
       <c r="AM2">
         <v>-161.8562887546276</v>
@@ -957,13 +957,13 @@
         <v>152.6722796269628</v>
       </c>
       <c r="AO2">
-        <v>5.678112598001612E-13</v>
+        <v>5.618423524074856E-13</v>
       </c>
       <c r="AP2">
         <v>179.999999999954</v>
       </c>
       <c r="AQ2">
-        <v>-179.9999999999594</v>
+        <v>-179.9999999999593</v>
       </c>
     </row>
   </sheetData>
@@ -1115,73 +1115,73 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>1.763086650584201</v>
+      </c>
+      <c r="D2">
         <v>1.763086650584198</v>
       </c>
-      <c r="D2">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>1.7630866505842</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1.763086650584199</v>
-      </c>
       <c r="G2">
-        <v>1.763086650584199</v>
+        <v>1.763086650584198</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>20.35837104638848</v>
+      </c>
+      <c r="J2">
         <v>20.35837104638846</v>
       </c>
-      <c r="J2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>20.35837104638847</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>20.35837104638846</v>
-      </c>
       <c r="M2">
-        <v>20.35837104638846</v>
+        <v>20.35837104638845</v>
       </c>
       <c r="N2">
-        <v>-5.21064684182868E-15</v>
+        <v>1.059100172792344E-29</v>
       </c>
       <c r="O2">
-        <v>19.07605560076268</v>
+        <v>19.07605560076271</v>
       </c>
       <c r="P2">
-        <v>-0.3008693307267478</v>
+        <v>-0.3008693307267407</v>
       </c>
       <c r="Q2">
-        <v>2.605323420914356E-15</v>
+        <v>-2.605323420914346E-15</v>
       </c>
       <c r="R2">
         <v>-17.45964880792891</v>
       </c>
       <c r="S2">
-        <v>1.917276123560547</v>
+        <v>1.917276123560536</v>
       </c>
       <c r="T2">
-        <v>-2.605323420914367E-15</v>
+        <v>-2.605323420914345E-15</v>
       </c>
       <c r="U2">
-        <v>3.991912765039866</v>
+        <v>3.991912765039879</v>
       </c>
       <c r="V2">
-        <v>15.21845990328568</v>
+        <v>15.21845990328566</v>
       </c>
       <c r="W2">
-        <v>-2.605323420914335E-15</v>
+        <v>-1.0869066822768E-29</v>
       </c>
       <c r="X2">
-        <v>-2.157912776816855</v>
+        <v>-2.157912776816863</v>
       </c>
       <c r="Y2">
-        <v>-13.38445991506266</v>
+        <v>-13.38445991506265</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1190,13 +1190,13 @@
         <v>-149.9129785515271</v>
       </c>
       <c r="AB2">
+        <v>30.08702144846562</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
         <v>30.0870214484656</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>30.08702144846563</v>
       </c>
       <c r="AE2">
         <v>-149.9129785515271</v>
@@ -1205,7 +1205,7 @@
         <v>1.100000023838388</v>
       </c>
       <c r="AG2">
-        <v>0.9573094133256668</v>
+        <v>0.9573094133256669</v>
       </c>
       <c r="AH2">
         <v>0.747674441885588</v>
@@ -1214,13 +1214,13 @@
         <v>1.100000023838388</v>
       </c>
       <c r="AJ2">
-        <v>0.8641406624621226</v>
+        <v>0.8641406624621223</v>
       </c>
       <c r="AK2">
-        <v>0.664153534610598</v>
+        <v>0.6641535346105982</v>
       </c>
       <c r="AL2">
-        <v>2.335896368299668E-13</v>
+        <v>2.329153052379138E-13</v>
       </c>
       <c r="AM2">
         <v>-138.0936484456564</v>
@@ -1229,13 +1229,13 @@
         <v>121.219612890337</v>
       </c>
       <c r="AO2">
-        <v>2.336918393575064E-13</v>
+        <v>2.390304601690072E-13</v>
       </c>
       <c r="AP2">
         <v>-142.8672784204023</v>
       </c>
       <c r="AQ2">
-        <v>128.2389811279578</v>
+        <v>128.2389811279577</v>
       </c>
     </row>
   </sheetData>
@@ -1387,112 +1387,112 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.763086650584201</v>
+        <v>1.763086650584198</v>
       </c>
       <c r="D2">
-        <v>1.7630866505842</v>
+        <v>1.763086650584198</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.7630866505842</v>
+        <v>1.763086650584197</v>
       </c>
       <c r="G2">
-        <v>1.763086650584199</v>
+        <v>1.763086650584198</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>20.35837104638848</v>
+        <v>20.35837104638845</v>
       </c>
       <c r="J2">
-        <v>20.35837104638847</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20.35837104638847</v>
+        <v>20.35837104638844</v>
       </c>
       <c r="M2">
         <v>20.35837104638846</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>-7.815970262743059E-15</v>
       </c>
       <c r="O2">
-        <v>19.0760556007627</v>
+        <v>19.07605560076267</v>
       </c>
       <c r="P2">
-        <v>-0.300869330726768</v>
+        <v>-0.3008693307267502</v>
       </c>
       <c r="Q2">
-        <v>-5.210646841828691E-15</v>
+        <v>5.210646841828701E-15</v>
       </c>
       <c r="R2">
-        <v>-17.4596488079289</v>
+        <v>-17.45964880792888</v>
       </c>
       <c r="S2">
-        <v>1.917276123560564</v>
+        <v>1.917276123560542</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>5.210646841828659E-15</v>
       </c>
       <c r="U2">
-        <v>3.991912765039902</v>
+        <v>3.991912765039876</v>
       </c>
       <c r="V2">
         <v>15.21845990328567</v>
       </c>
       <c r="W2">
-        <v>-2.161335190834621E-29</v>
+        <v>-2.605323420914324E-15</v>
       </c>
       <c r="X2">
-        <v>-2.157912776816886</v>
+        <v>-2.15791277681687</v>
       </c>
       <c r="Y2">
-        <v>-13.38445991506265</v>
+        <v>-13.38445991506266</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-149.9129785515272</v>
+        <v>-149.9129785515271</v>
       </c>
       <c r="AB2">
-        <v>30.08702144846554</v>
+        <v>30.08702144846559</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>30.08702144846553</v>
+        <v>30.0870214484656</v>
       </c>
       <c r="AE2">
-        <v>-149.9129785515272</v>
+        <v>-149.9129785515271</v>
       </c>
       <c r="AF2">
         <v>1.100000023838388</v>
       </c>
       <c r="AG2">
-        <v>0.9573094133256665</v>
+        <v>0.9573094133256668</v>
       </c>
       <c r="AH2">
-        <v>0.7476744418855877</v>
+        <v>0.7476744418855882</v>
       </c>
       <c r="AI2">
         <v>1.100000023838388</v>
       </c>
       <c r="AJ2">
-        <v>0.8641406624621222</v>
+        <v>0.8641406624621225</v>
       </c>
       <c r="AK2">
-        <v>0.6641535346105981</v>
+        <v>0.6641535346105983</v>
       </c>
       <c r="AL2">
-        <v>2.346361573717963E-13</v>
+        <v>2.319016547530173E-13</v>
       </c>
       <c r="AM2">
         <v>-138.0936484456564</v>
@@ -1501,7 +1501,7 @@
         <v>121.219612890337</v>
       </c>
       <c r="AO2">
-        <v>2.376583719967879E-13</v>
+        <v>2.353929266461961E-13</v>
       </c>
       <c r="AP2">
         <v>-142.8672784204022</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.11908582522893</v>
+        <v>3.119085825228932</v>
       </c>
       <c r="D2">
         <v>3.119085825228932</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.11908582522893</v>
+        <v>3.119085825228932</v>
       </c>
       <c r="G2">
         <v>3.119085825228932</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>36.01610081642937</v>
+        <v>36.01610081642941</v>
       </c>
       <c r="J2">
         <v>36.0161008164294</v>
@@ -1686,46 +1686,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>36.01610081642937</v>
+        <v>36.0161008164294</v>
       </c>
       <c r="M2">
-        <v>36.01610081642941</v>
+        <v>36.0161008164294</v>
       </c>
       <c r="N2">
-        <v>-9.473903143508922E-15</v>
+        <v>-2.36847578587712E-15</v>
       </c>
       <c r="O2">
-        <v>26.59966124765505</v>
+        <v>26.59966124765508</v>
       </c>
       <c r="P2">
-        <v>-7.17339990489539</v>
+        <v>-7.173399904895398</v>
       </c>
       <c r="Q2">
-        <v>9.473903143508969E-15</v>
+        <v>2.368475785877073E-15</v>
       </c>
       <c r="R2">
-        <v>-16.8865305763223</v>
+        <v>-16.88653057632229</v>
       </c>
       <c r="S2">
-        <v>16.88653057622837</v>
+        <v>16.88653057622835</v>
       </c>
       <c r="T2">
-        <v>9.473903143508737E-15</v>
+        <v>-9.473903143508857E-15</v>
       </c>
       <c r="U2">
-        <v>-0.5158635800632538</v>
+        <v>-0.5158635800632787</v>
       </c>
       <c r="V2">
         <v>11.9957253844309</v>
       </c>
       <c r="W2">
-        <v>-1.421085471526315E-14</v>
+        <v>1.421085471526328E-14</v>
       </c>
       <c r="X2">
-        <v>6.255794482090772</v>
+        <v>6.255794482090788</v>
       </c>
       <c r="Y2">
-        <v>-6.255794482403464</v>
+        <v>-6.255794482403469</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1734,7 +1734,7 @@
         <v>-159.6723164477259</v>
       </c>
       <c r="AB2">
-        <v>20.32768355226676</v>
+        <v>20.32768355226675</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1746,40 +1746,40 @@
         <v>-159.672316447726</v>
       </c>
       <c r="AF2">
-        <v>1.000000000004309</v>
+        <v>1.00000000000431</v>
       </c>
       <c r="AG2">
-        <v>0.7386880424046125</v>
+        <v>0.7386880424046126</v>
       </c>
       <c r="AH2">
-        <v>0.3880750091708056</v>
+        <v>0.3880750091708058</v>
       </c>
       <c r="AI2">
-        <v>1.000000000004309</v>
+        <v>1.00000000000431</v>
       </c>
       <c r="AJ2">
-        <v>0.5000000000018687</v>
+        <v>0.5000000000018683</v>
       </c>
       <c r="AK2">
-        <v>0.5000000000024387</v>
+        <v>0.5000000000024385</v>
       </c>
       <c r="AL2">
-        <v>5.540780593410937E-13</v>
+        <v>5.36398253571908E-13</v>
       </c>
       <c r="AM2">
-        <v>-160.7833494395999</v>
+        <v>-160.7833494396</v>
       </c>
       <c r="AN2">
         <v>141.2069528724241</v>
       </c>
       <c r="AO2">
-        <v>5.724680649065084E-13</v>
+        <v>5.484345603695309E-13</v>
       </c>
       <c r="AP2">
         <v>-179.9999999994768</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999994719</v>
+        <v>179.9999999994718</v>
       </c>
     </row>
   </sheetData>
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.11908582522893</v>
+        <v>3.119085825228932</v>
       </c>
       <c r="D2">
         <v>3.119085825228932</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.11908582522893</v>
+        <v>3.119085825228932</v>
       </c>
       <c r="G2">
         <v>3.119085825228932</v>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>36.01610081642937</v>
+        <v>36.01610081642941</v>
       </c>
       <c r="J2">
         <v>36.0161008164294</v>
@@ -1958,46 +1958,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>36.01610081642937</v>
+        <v>36.0161008164294</v>
       </c>
       <c r="M2">
-        <v>36.01610081642941</v>
+        <v>36.0161008164294</v>
       </c>
       <c r="N2">
-        <v>-9.473903143508922E-15</v>
+        <v>-2.36847578587712E-15</v>
       </c>
       <c r="O2">
-        <v>26.59966124765505</v>
+        <v>26.59966124765508</v>
       </c>
       <c r="P2">
-        <v>-7.17339990489539</v>
+        <v>-7.173399904895398</v>
       </c>
       <c r="Q2">
-        <v>9.473903143508969E-15</v>
+        <v>2.368475785877073E-15</v>
       </c>
       <c r="R2">
-        <v>-16.8865305763223</v>
+        <v>-16.88653057632229</v>
       </c>
       <c r="S2">
-        <v>16.88653057622837</v>
+        <v>16.88653057622835</v>
       </c>
       <c r="T2">
-        <v>9.473903143508737E-15</v>
+        <v>-9.473903143508857E-15</v>
       </c>
       <c r="U2">
-        <v>-0.5158635800632538</v>
+        <v>-0.5158635800632787</v>
       </c>
       <c r="V2">
         <v>11.9957253844309</v>
       </c>
       <c r="W2">
-        <v>-1.421085471526315E-14</v>
+        <v>1.421085471526328E-14</v>
       </c>
       <c r="X2">
-        <v>6.255794482090772</v>
+        <v>6.255794482090788</v>
       </c>
       <c r="Y2">
-        <v>-6.255794482403464</v>
+        <v>-6.255794482403469</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>-159.6723164477259</v>
       </c>
       <c r="AB2">
-        <v>20.32768355226676</v>
+        <v>20.32768355226675</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -2018,40 +2018,40 @@
         <v>-159.672316447726</v>
       </c>
       <c r="AF2">
-        <v>1.000000000004309</v>
+        <v>1.00000000000431</v>
       </c>
       <c r="AG2">
-        <v>0.7386880424046125</v>
+        <v>0.7386880424046126</v>
       </c>
       <c r="AH2">
-        <v>0.3880750091708056</v>
+        <v>0.3880750091708058</v>
       </c>
       <c r="AI2">
-        <v>1.000000000004309</v>
+        <v>1.00000000000431</v>
       </c>
       <c r="AJ2">
-        <v>0.5000000000018687</v>
+        <v>0.5000000000018683</v>
       </c>
       <c r="AK2">
-        <v>0.5000000000024387</v>
+        <v>0.5000000000024385</v>
       </c>
       <c r="AL2">
-        <v>5.540780593410937E-13</v>
+        <v>5.36398253571908E-13</v>
       </c>
       <c r="AM2">
-        <v>-160.7833494395999</v>
+        <v>-160.7833494396</v>
       </c>
       <c r="AN2">
         <v>141.2069528724241</v>
       </c>
       <c r="AO2">
-        <v>5.724680649065084E-13</v>
+        <v>5.484345603695309E-13</v>
       </c>
       <c r="AP2">
         <v>-179.9999999994768</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999994719</v>
+        <v>179.9999999994718</v>
       </c>
     </row>
   </sheetData>
@@ -2206,67 +2206,67 @@
         <v>1.518298438953096</v>
       </c>
       <c r="D2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="G2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>17.53180024879518</v>
+      </c>
+      <c r="J2">
+        <v>17.53180024879518</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>17.53180024879518</v>
+      </c>
+      <c r="M2">
         <v>17.53180024879517</v>
       </c>
-      <c r="J2">
-        <v>17.53180024879516</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>17.53180024879516</v>
-      </c>
-      <c r="M2">
-        <v>17.53180024879516</v>
-      </c>
       <c r="N2">
-        <v>1.776356839406665E-15</v>
+        <v>-2.368475785875557E-15</v>
       </c>
       <c r="O2">
-        <v>15.39322071800312</v>
+        <v>15.39322071800313</v>
       </c>
       <c r="P2">
-        <v>0.7360136868429302</v>
+        <v>0.7360136868429367</v>
       </c>
       <c r="Q2">
-        <v>-1.776356839406654E-15</v>
+        <v>5.921189464688919E-16</v>
       </c>
       <c r="R2">
-        <v>-13.091678889029</v>
+        <v>-13.09167888902901</v>
       </c>
       <c r="S2">
-        <v>1.565528142131215</v>
+        <v>1.565528142131213</v>
       </c>
       <c r="T2">
-        <v>2.368475785875574E-15</v>
+        <v>-2.368475785875577E-15</v>
       </c>
       <c r="U2">
-        <v>2.313527558708349</v>
+        <v>2.313527558708351</v>
       </c>
       <c r="V2">
-        <v>11.93279478711934</v>
+        <v>11.93279478711935</v>
       </c>
       <c r="W2">
-        <v>-4.736951571751141E-15</v>
+        <v>2.523264953486208E-30</v>
       </c>
       <c r="X2">
-        <v>-0.9534417621250361</v>
+        <v>-0.953441762125029</v>
       </c>
       <c r="Y2">
         <v>-10.57270899053605</v>
@@ -2278,13 +2278,13 @@
         <v>-146.723813863879</v>
       </c>
       <c r="AB2">
-        <v>33.27618613611368</v>
+        <v>33.27618613611372</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>33.2761861361137</v>
+        <v>33.27618613611372</v>
       </c>
       <c r="AE2">
         <v>-146.723813863879</v>
@@ -2296,19 +2296,19 @@
         <v>0.8878783530243616</v>
       </c>
       <c r="AH2">
-        <v>0.681930645912687</v>
+        <v>0.6819306459126869</v>
       </c>
       <c r="AI2">
         <v>1.000000000003617</v>
       </c>
       <c r="AJ2">
-        <v>0.748716700614258</v>
+        <v>0.7487167006142578</v>
       </c>
       <c r="AK2">
-        <v>0.609634280027363</v>
+        <v>0.6096342800273626</v>
       </c>
       <c r="AL2">
-        <v>2.446768151228995E-13</v>
+        <v>2.390358747421595E-13</v>
       </c>
       <c r="AM2">
         <v>-138.1765060860386</v>
@@ -2317,7 +2317,7 @@
         <v>119.7466591084986</v>
       </c>
       <c r="AO2">
-        <v>2.534562525862115E-13</v>
+        <v>2.44161132303209E-13</v>
       </c>
       <c r="AP2">
         <v>-142.5584264979142</v>
@@ -2478,67 +2478,67 @@
         <v>1.518298438953096</v>
       </c>
       <c r="D2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="G2">
-        <v>1.518298438953095</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
+        <v>17.53180024879518</v>
+      </c>
+      <c r="J2">
+        <v>17.53180024879518</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>17.53180024879518</v>
+      </c>
+      <c r="M2">
         <v>17.53180024879517</v>
       </c>
-      <c r="J2">
-        <v>17.53180024879516</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>17.53180024879516</v>
-      </c>
-      <c r="M2">
-        <v>17.53180024879516</v>
-      </c>
       <c r="N2">
-        <v>1.776356839406665E-15</v>
+        <v>-2.368475785875557E-15</v>
       </c>
       <c r="O2">
-        <v>15.39322071800312</v>
+        <v>15.39322071800313</v>
       </c>
       <c r="P2">
-        <v>0.7360136868429302</v>
+        <v>0.7360136868429367</v>
       </c>
       <c r="Q2">
-        <v>-1.776356839406654E-15</v>
+        <v>5.921189464688919E-16</v>
       </c>
       <c r="R2">
-        <v>-13.091678889029</v>
+        <v>-13.09167888902901</v>
       </c>
       <c r="S2">
-        <v>1.565528142131215</v>
+        <v>1.565528142131213</v>
       </c>
       <c r="T2">
-        <v>2.368475785875574E-15</v>
+        <v>-2.368475785875577E-15</v>
       </c>
       <c r="U2">
-        <v>2.313527558708349</v>
+        <v>2.313527558708351</v>
       </c>
       <c r="V2">
-        <v>11.93279478711934</v>
+        <v>11.93279478711935</v>
       </c>
       <c r="W2">
-        <v>-4.736951571751141E-15</v>
+        <v>2.523264953486208E-30</v>
       </c>
       <c r="X2">
-        <v>-0.9534417621250361</v>
+        <v>-0.953441762125029</v>
       </c>
       <c r="Y2">
         <v>-10.57270899053605</v>
@@ -2550,13 +2550,13 @@
         <v>-146.723813863879</v>
       </c>
       <c r="AB2">
-        <v>33.27618613611368</v>
+        <v>33.27618613611372</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>33.2761861361137</v>
+        <v>33.27618613611372</v>
       </c>
       <c r="AE2">
         <v>-146.723813863879</v>
@@ -2568,19 +2568,19 @@
         <v>0.8878783530243616</v>
       </c>
       <c r="AH2">
-        <v>0.681930645912687</v>
+        <v>0.6819306459126869</v>
       </c>
       <c r="AI2">
         <v>1.000000000003617</v>
       </c>
       <c r="AJ2">
-        <v>0.748716700614258</v>
+        <v>0.7487167006142578</v>
       </c>
       <c r="AK2">
-        <v>0.609634280027363</v>
+        <v>0.6096342800273626</v>
       </c>
       <c r="AL2">
-        <v>2.446768151228995E-13</v>
+        <v>2.390358747421595E-13</v>
       </c>
       <c r="AM2">
         <v>-138.1765060860386</v>
@@ -2589,7 +2589,7 @@
         <v>119.7466591084986</v>
       </c>
       <c r="AO2">
-        <v>2.534562525862115E-13</v>
+        <v>2.44161132303209E-13</v>
       </c>
       <c r="AP2">
         <v>-142.5584264979142</v>
@@ -2747,13 +2747,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.150115884676075</v>
+        <v>4.150115884676072</v>
       </c>
       <c r="C2">
-        <v>0.001307688437078765</v>
+        <v>0.001307688437079183</v>
       </c>
       <c r="D2">
-        <v>0.001307688437079984</v>
+        <v>0.001307688437078827</v>
       </c>
       <c r="E2">
         <v>4.149403057445678</v>
@@ -2765,13 +2765,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>47.92141046371748</v>
+        <v>47.92141046371745</v>
       </c>
       <c r="I2">
-        <v>0.01509988542327172</v>
+        <v>0.01509988542327654</v>
       </c>
       <c r="J2">
-        <v>0.01509988542328579</v>
+        <v>0.01509988542327243</v>
       </c>
       <c r="K2">
         <v>47.91317944385037</v>
@@ -2783,52 +2783,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>27.19116803012082</v>
+        <v>27.1911680301208</v>
       </c>
       <c r="O2">
-        <v>0.01384375142256182</v>
+        <v>0.01384375142256535</v>
       </c>
       <c r="P2">
-        <v>-0.01236983620741903</v>
+        <v>-0.01236983620739555</v>
       </c>
       <c r="Q2">
-        <v>3.097741397554418E-10</v>
+        <v>3.097602395867177E-10</v>
       </c>
       <c r="R2">
-        <v>1.230990548529609E-10</v>
+        <v>1.230812512493562E-10</v>
       </c>
       <c r="S2">
-        <v>-1.286643278131962E-08</v>
+        <v>-1.286646085906846E-08</v>
       </c>
       <c r="T2">
-        <v>15.20531856971823</v>
+        <v>15.20531856971821</v>
       </c>
       <c r="U2">
-        <v>0.0003364971267661923</v>
+        <v>0.0003364971268024312</v>
       </c>
       <c r="V2">
-        <v>-0.01151726172505387</v>
+        <v>-0.01151726172505715</v>
       </c>
       <c r="W2">
-        <v>-3.679065670482516E-10</v>
+        <v>-3.679102972557161E-10</v>
       </c>
       <c r="X2">
-        <v>-7.861129686417365E-09</v>
+        <v>-7.861159407178003E-09</v>
       </c>
       <c r="Y2">
-        <v>3.3614250792894E-09</v>
+        <v>3.361434646228529E-09</v>
       </c>
       <c r="Z2">
-        <v>-57.37178929740404</v>
+        <v>-57.37178929740406</v>
       </c>
       <c r="AA2">
-        <v>-114.3324366242245</v>
+        <v>-114.332436624374</v>
       </c>
       <c r="AB2">
-        <v>-114.332436624299</v>
+        <v>-114.3324366243613</v>
       </c>
       <c r="AC2">
-        <v>122.6433476673686</v>
+        <v>122.6433476673685</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.650102595822785</v>
+        <v>0.6501025958227847</v>
       </c>
       <c r="AH2">
-        <v>0.9170824819277787</v>
+        <v>0.9170824819277784</v>
       </c>
       <c r="AI2">
         <v>1.119312077258385</v>
@@ -2849,13 +2849,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.8726123019582072</v>
+        <v>0.8726123019582064</v>
       </c>
       <c r="AL2">
         <v>1.475971874091154</v>
       </c>
       <c r="AM2">
-        <v>-28.15784081640619</v>
+        <v>-28.15784081640621</v>
       </c>
       <c r="AN2">
         <v>-112.940034452093</v>
@@ -3022,16 +3022,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.150115884676075</v>
+        <v>4.150115884676071</v>
       </c>
       <c r="C2">
-        <v>0.001307688437078266</v>
+        <v>0.001307688437078929</v>
       </c>
       <c r="D2">
-        <v>0.001307688437079877</v>
+        <v>0.00130768843707961</v>
       </c>
       <c r="E2">
-        <v>4.149403057445681</v>
+        <v>4.149403057445676</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3040,16 +3040,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>47.92141046371748</v>
+        <v>47.92141046371742</v>
       </c>
       <c r="I2">
-        <v>0.01509988542326596</v>
+        <v>0.01509988542327361</v>
       </c>
       <c r="J2">
-        <v>0.01509988542328456</v>
+        <v>0.01509988542328148</v>
       </c>
       <c r="K2">
-        <v>47.9131794438504</v>
+        <v>47.91317944385035</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3058,52 +3058,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>27.19116803012085</v>
+        <v>27.1911680301208</v>
       </c>
       <c r="O2">
-        <v>0.01384375142255566</v>
+        <v>0.01384375142256281</v>
       </c>
       <c r="P2">
-        <v>-0.0123698362073938</v>
+        <v>-0.01236983620741401</v>
       </c>
       <c r="Q2">
-        <v>3.097300992981633E-10</v>
+        <v>3.097386335427153E-10</v>
       </c>
       <c r="R2">
-        <v>1.230912138603286E-10</v>
+        <v>1.230886299421973E-10</v>
       </c>
       <c r="S2">
-        <v>-1.286646373651391E-08</v>
+        <v>-1.286644203672448E-08</v>
       </c>
       <c r="T2">
         <v>15.20531856971822</v>
       </c>
       <c r="U2">
-        <v>0.0003364971268018137</v>
+        <v>0.0003364971267964297</v>
       </c>
       <c r="V2">
-        <v>-0.01151726172507894</v>
+        <v>-0.01151726172505218</v>
       </c>
       <c r="W2">
-        <v>-3.679036241530959E-10</v>
+        <v>-3.679217256928126E-10</v>
       </c>
       <c r="X2">
-        <v>-7.861164369024982E-09</v>
+        <v>-7.861158365827348E-09</v>
       </c>
       <c r="Y2">
-        <v>3.361472187071751E-09</v>
+        <v>3.361443901633388E-09</v>
       </c>
       <c r="Z2">
         <v>-57.37178929740404</v>
       </c>
       <c r="AA2">
-        <v>-114.3324366243725</v>
+        <v>-114.3324366243495</v>
       </c>
       <c r="AB2">
-        <v>-114.3324366244195</v>
+        <v>-114.3324366243064</v>
       </c>
       <c r="AC2">
-        <v>122.6433476673686</v>
+        <v>122.6433476673685</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6501025958227853</v>
+        <v>0.6501025958227851</v>
       </c>
       <c r="AH2">
         <v>0.9170824819277785</v>
@@ -3124,13 +3124,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.8726123019582068</v>
+        <v>0.8726123019582067</v>
       </c>
       <c r="AL2">
         <v>1.475971874091154</v>
       </c>
       <c r="AM2">
-        <v>-28.15784081640622</v>
+        <v>-28.1578408164062</v>
       </c>
       <c r="AN2">
         <v>-112.940034452093</v>
@@ -3300,13 +3300,13 @@
         <v>1.259987556201641</v>
       </c>
       <c r="C2">
-        <v>0.0003970181083843863</v>
+        <v>0.0003970181083841795</v>
       </c>
       <c r="D2">
-        <v>0.0003970181083843431</v>
+        <v>0.0003970181083840901</v>
       </c>
       <c r="E2">
-        <v>1.259771139729192</v>
+        <v>1.259771139729191</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3315,13 +3315,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>14.54908309497193</v>
+        <v>14.54908309497192</v>
       </c>
       <c r="I2">
-        <v>0.004584370234977629</v>
+        <v>0.004584370234975241</v>
       </c>
       <c r="J2">
-        <v>0.004584370234977131</v>
+        <v>0.004584370234974209</v>
       </c>
       <c r="K2">
         <v>14.54658413279941</v>
@@ -3336,49 +3336,49 @@
         <v>10.44072245344139</v>
       </c>
       <c r="O2">
-        <v>0.004639096867849978</v>
+        <v>0.004639096867849144</v>
       </c>
       <c r="P2">
-        <v>-0.003769398968301289</v>
+        <v>-0.003769398968300112</v>
       </c>
       <c r="Q2">
-        <v>-7.935116622230361</v>
+        <v>-7.935116622230355</v>
       </c>
       <c r="R2">
-        <v>2.618362121632441E-10</v>
+        <v>2.618338511963502E-10</v>
       </c>
       <c r="S2">
-        <v>-3.125799116517588E-09</v>
+        <v>-3.125802013758014E-09</v>
       </c>
       <c r="T2">
-        <v>9.340123010958134</v>
+        <v>9.340123010958138</v>
       </c>
       <c r="U2">
-        <v>-0.001063277019730574</v>
+        <v>-0.001063277019723117</v>
       </c>
       <c r="V2">
-        <v>-0.003426942863138502</v>
+        <v>-0.00342694286313497</v>
       </c>
       <c r="W2">
         <v>-7.935116626504435</v>
       </c>
       <c r="X2">
-        <v>-2.819910253628664E-09</v>
+        <v>-2.819922095966884E-09</v>
       </c>
       <c r="Y2">
-        <v>1.140569294315215E-09</v>
+        <v>1.14056270011847E-09</v>
       </c>
       <c r="Z2">
-        <v>-48.74026366666283</v>
+        <v>-48.74026366666286</v>
       </c>
       <c r="AA2">
-        <v>-105.7009109935136</v>
+        <v>-105.7009109935989</v>
       </c>
       <c r="AB2">
-        <v>-105.7009109935461</v>
+        <v>-105.7009109935256</v>
       </c>
       <c r="AC2">
-        <v>131.2748732981098</v>
+        <v>131.2748732981097</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9628650605449166</v>
+        <v>0.9628650605449164</v>
       </c>
       <c r="AH2">
         <v>1.038177140583</v>
@@ -3405,7 +3405,7 @@
         <v>1.2164108368883</v>
       </c>
       <c r="AM2">
-        <v>-6.924897553952472</v>
+        <v>-6.924897553952477</v>
       </c>
       <c r="AN2">
         <v>-118.6100874847788</v>
@@ -3491,49 +3491,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.282962610066689</v>
+        <v>4.282962610066681</v>
       </c>
       <c r="C2">
-        <v>4.282962610066689</v>
+        <v>4.282962610066681</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.277811204449911</v>
+        <v>9.27781120444989</v>
       </c>
       <c r="F2">
-        <v>148.3661769510663</v>
+        <v>148.366176951066</v>
       </c>
       <c r="G2">
-        <v>148.3661769510663</v>
+        <v>148.366176951066</v>
       </c>
       <c r="H2">
-        <v>28.61627979050458</v>
+        <v>28.61627979050424</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>32.46847082824958</v>
+        <v>32.46847082824999</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-77.779845794214</v>
+        <v>-77.77984579421411</v>
       </c>
       <c r="M2">
-        <v>102.2201542057787</v>
+        <v>102.2201542057786</v>
       </c>
       <c r="N2">
-        <v>0.2917056037382955</v>
+        <v>0.2917056037382966</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-29.1713773552608</v>
+        <v>-29.17137735526021</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -3688,16 +3688,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.259987556201643</v>
+        <v>1.259987556201642</v>
       </c>
       <c r="C2">
-        <v>0.0003970181083838124</v>
+        <v>0.0003970181083835949</v>
       </c>
       <c r="D2">
-        <v>0.0003970181083843399</v>
+        <v>0.0003970181083841456</v>
       </c>
       <c r="E2">
-        <v>1.259771139729192</v>
+        <v>1.259771139729193</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3706,13 +3706,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>14.54908309497194</v>
+        <v>14.54908309497193</v>
       </c>
       <c r="I2">
-        <v>0.004584370234971002</v>
+        <v>0.00458437023496849</v>
       </c>
       <c r="J2">
-        <v>0.004584370234977093</v>
+        <v>0.00458437023497485</v>
       </c>
       <c r="K2">
         <v>14.54658413279942</v>
@@ -3727,46 +3727,46 @@
         <v>10.4407224534414</v>
       </c>
       <c r="O2">
-        <v>0.004639096867845415</v>
+        <v>0.004639096867842325</v>
       </c>
       <c r="P2">
-        <v>-0.003769398968294814</v>
+        <v>-0.003769398968298936</v>
       </c>
       <c r="Q2">
-        <v>-7.935116622230368</v>
+        <v>-7.935116622230371</v>
       </c>
       <c r="R2">
-        <v>2.618404797680886E-10</v>
+        <v>2.618428362977824E-10</v>
       </c>
       <c r="S2">
-        <v>-3.125811597508452E-09</v>
+        <v>-3.125806645690055E-09</v>
       </c>
       <c r="T2">
-        <v>9.340123010958143</v>
+        <v>9.340123010958138</v>
       </c>
       <c r="U2">
-        <v>-0.001063277019719683</v>
+        <v>-0.001063277019721498</v>
       </c>
       <c r="V2">
-        <v>-0.003426942863145563</v>
+        <v>-0.003426942863137325</v>
       </c>
       <c r="W2">
         <v>-7.935116626504437</v>
       </c>
       <c r="X2">
-        <v>-2.819922275036141E-09</v>
+        <v>-2.819923189134303E-09</v>
       </c>
       <c r="Y2">
-        <v>1.140573833933992E-09</v>
+        <v>1.140565049899447E-09</v>
       </c>
       <c r="Z2">
         <v>-48.74026366666283</v>
       </c>
       <c r="AA2">
-        <v>-105.7009109936291</v>
+        <v>-105.7009109935995</v>
       </c>
       <c r="AB2">
-        <v>-105.7009109936538</v>
+        <v>-105.7009109935541</v>
       </c>
       <c r="AC2">
         <v>131.2748732981098</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9628650605449166</v>
+        <v>0.9628650605449167</v>
       </c>
       <c r="AH2">
         <v>1.038177140583</v>
@@ -3796,7 +3796,7 @@
         <v>1.2164108368883</v>
       </c>
       <c r="AM2">
-        <v>-6.924897553952482</v>
+        <v>-6.924897553952481</v>
       </c>
       <c r="AN2">
         <v>-118.6100874847788</v>
@@ -3805,7 +3805,7 @@
         <v>116.5745799757034</v>
       </c>
       <c r="AP2">
-        <v>-3.725126686454231</v>
+        <v>-3.725126686454236</v>
       </c>
       <c r="AQ2">
         <v>-125.2375227398212</v>
@@ -3966,13 +3966,13 @@
         <v>2.826503590882588</v>
       </c>
       <c r="C2">
-        <v>0.001514726880395789</v>
+        <v>0.001514726880396092</v>
       </c>
       <c r="D2">
-        <v>0.001514726880394834</v>
+        <v>0.001514726880395903</v>
       </c>
       <c r="E2">
-        <v>2.826014554613982</v>
+        <v>2.826014554613983</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3984,13 +3984,13 @@
         <v>32.63765218123012</v>
       </c>
       <c r="I2">
-        <v>0.01749055944290542</v>
+        <v>0.01749055944290891</v>
       </c>
       <c r="J2">
-        <v>0.01749055944289439</v>
+        <v>0.01749055944290673</v>
       </c>
       <c r="K2">
-        <v>32.63200527680365</v>
+        <v>32.63200527680367</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3999,52 +3999,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>24.21629159096678</v>
+        <v>24.21629159096677</v>
       </c>
       <c r="O2">
-        <v>0.01474207751742179</v>
+        <v>0.01474207751742549</v>
       </c>
       <c r="P2">
-        <v>-0.01341928711891293</v>
+        <v>-0.01341928711892778</v>
       </c>
       <c r="Q2">
-        <v>-9.785572747805895E-11</v>
+        <v>-9.782346681605147E-11</v>
       </c>
       <c r="R2">
-        <v>-4.308155123457532E-09</v>
+        <v>-4.308159163536519E-09</v>
       </c>
       <c r="S2">
-        <v>-1.647191241025048E-08</v>
+        <v>-1.647189079812664E-08</v>
       </c>
       <c r="T2">
-        <v>7.041002540869046</v>
+        <v>7.04100254086907</v>
       </c>
       <c r="U2">
-        <v>-0.001500030071442015</v>
+        <v>-0.001500030071434891</v>
       </c>
       <c r="V2">
-        <v>-0.01266679104743506</v>
+        <v>-0.01266679104743828</v>
       </c>
       <c r="W2">
-        <v>1.240208456132686E-11</v>
+        <v>1.238099844068448E-11</v>
       </c>
       <c r="X2">
-        <v>-1.028676414356934E-08</v>
+        <v>-1.028676392862464E-08</v>
       </c>
       <c r="Y2">
-        <v>6.07311812558078E-09</v>
+        <v>6.073123793463956E-09</v>
       </c>
       <c r="Z2">
-        <v>-40.47982361172814</v>
+        <v>-40.47982361172819</v>
       </c>
       <c r="AA2">
-        <v>-111.629697085513</v>
+        <v>-111.6296970855418</v>
       </c>
       <c r="AB2">
-        <v>-111.6296970855482</v>
+        <v>-111.6296970855238</v>
       </c>
       <c r="AC2">
-        <v>139.5492395016656</v>
+        <v>139.5492395016655</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7727004812958143</v>
+        <v>0.772700481295814</v>
       </c>
       <c r="AH2">
         <v>0.8472111075846839</v>
@@ -4065,13 +4065,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.9475300844110904</v>
+        <v>0.94753008441109</v>
       </c>
       <c r="AL2">
-        <v>1.49156495202401</v>
+        <v>1.491564952024011</v>
       </c>
       <c r="AM2">
-        <v>-24.26778175483754</v>
+        <v>-24.26778175483753</v>
       </c>
       <c r="AN2">
         <v>-117.4396388970154</v>
@@ -4241,13 +4241,13 @@
         <v>2.826503590882588</v>
       </c>
       <c r="C2">
-        <v>0.001514726880395789</v>
+        <v>0.001514726880396092</v>
       </c>
       <c r="D2">
-        <v>0.001514726880394834</v>
+        <v>0.001514726880395903</v>
       </c>
       <c r="E2">
-        <v>2.826014554613982</v>
+        <v>2.826014554613983</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4259,13 +4259,13 @@
         <v>32.63765218123012</v>
       </c>
       <c r="I2">
-        <v>0.01749055944290542</v>
+        <v>0.01749055944290891</v>
       </c>
       <c r="J2">
-        <v>0.01749055944289439</v>
+        <v>0.01749055944290673</v>
       </c>
       <c r="K2">
-        <v>32.63200527680365</v>
+        <v>32.63200527680367</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4274,52 +4274,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>24.21629159096678</v>
+        <v>24.21629159096677</v>
       </c>
       <c r="O2">
-        <v>0.01474207751742179</v>
+        <v>0.01474207751742549</v>
       </c>
       <c r="P2">
-        <v>-0.01341928711891293</v>
+        <v>-0.01341928711892778</v>
       </c>
       <c r="Q2">
-        <v>-9.785572747805895E-11</v>
+        <v>-9.782346681605147E-11</v>
       </c>
       <c r="R2">
-        <v>-4.308155123457532E-09</v>
+        <v>-4.308159163536519E-09</v>
       </c>
       <c r="S2">
-        <v>-1.647191241025048E-08</v>
+        <v>-1.647189079812664E-08</v>
       </c>
       <c r="T2">
-        <v>7.041002540869046</v>
+        <v>7.04100254086907</v>
       </c>
       <c r="U2">
-        <v>-0.001500030071442015</v>
+        <v>-0.001500030071434891</v>
       </c>
       <c r="V2">
-        <v>-0.01266679104743506</v>
+        <v>-0.01266679104743828</v>
       </c>
       <c r="W2">
-        <v>1.240208456132686E-11</v>
+        <v>1.238099844068448E-11</v>
       </c>
       <c r="X2">
-        <v>-1.028676414356934E-08</v>
+        <v>-1.028676392862464E-08</v>
       </c>
       <c r="Y2">
-        <v>6.07311812558078E-09</v>
+        <v>6.073123793463956E-09</v>
       </c>
       <c r="Z2">
-        <v>-40.47982361172814</v>
+        <v>-40.47982361172819</v>
       </c>
       <c r="AA2">
-        <v>-111.629697085513</v>
+        <v>-111.6296970855418</v>
       </c>
       <c r="AB2">
-        <v>-111.6296970855482</v>
+        <v>-111.6296970855238</v>
       </c>
       <c r="AC2">
-        <v>139.5492395016656</v>
+        <v>139.5492395016655</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7727004812958143</v>
+        <v>0.772700481295814</v>
       </c>
       <c r="AH2">
         <v>0.8472111075846839</v>
@@ -4340,13 +4340,13 @@
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.9475300844110904</v>
+        <v>0.94753008441109</v>
       </c>
       <c r="AL2">
-        <v>1.49156495202401</v>
+        <v>1.491564952024011</v>
       </c>
       <c r="AM2">
-        <v>-24.26778175483754</v>
+        <v>-24.26778175483753</v>
       </c>
       <c r="AN2">
         <v>-117.4396388970154</v>
@@ -4516,10 +4516,10 @@
         <v>1.035889633734118</v>
       </c>
       <c r="C2">
-        <v>0.0005551345763019315</v>
+        <v>0.0005551345763019103</v>
       </c>
       <c r="D2">
-        <v>0.0005551345763016516</v>
+        <v>0.0005551345763019823</v>
       </c>
       <c r="E2">
         <v>1.035710406082399</v>
@@ -4534,10 +4534,10 @@
         <v>11.96142317774272</v>
       </c>
       <c r="I2">
-        <v>0.006410141941287781</v>
+        <v>0.006410141941287535</v>
       </c>
       <c r="J2">
-        <v>0.006410141941284548</v>
+        <v>0.006410141941288367</v>
       </c>
       <c r="K2">
         <v>11.9593536350834</v>
@@ -4549,49 +4549,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>8.61432307590413</v>
+        <v>8.614323075904119</v>
       </c>
       <c r="O2">
-        <v>0.006036631569588754</v>
+        <v>0.006036631569588482</v>
       </c>
       <c r="P2">
-        <v>-0.004065327085942332</v>
+        <v>-0.004065327085947163</v>
       </c>
       <c r="Q2">
-        <v>-5.363480227314734</v>
+        <v>-5.363480227314723</v>
       </c>
       <c r="R2">
-        <v>-4.817115396587726E-11</v>
+        <v>-4.817393985560517E-11</v>
       </c>
       <c r="S2">
-        <v>-4.802057520624759E-09</v>
+        <v>-4.802052006224878E-09</v>
       </c>
       <c r="T2">
-        <v>6.312848364667321</v>
+        <v>6.312848364667334</v>
       </c>
       <c r="U2">
-        <v>-0.0004724106998723624</v>
+        <v>-0.0004724106998728516</v>
       </c>
       <c r="V2">
-        <v>-0.005078948493509238</v>
+        <v>-0.005078948493510333</v>
       </c>
       <c r="W2">
-        <v>-5.36348023021802</v>
+        <v>-5.363480230218032</v>
       </c>
       <c r="X2">
-        <v>-4.065631023489448E-09</v>
+        <v>-4.065630861704757E-09</v>
       </c>
       <c r="Y2">
-        <v>1.698281583200238E-09</v>
+        <v>1.69828326623497E-09</v>
       </c>
       <c r="Z2">
-        <v>-43.36332196693328</v>
+        <v>-43.36332196693336</v>
       </c>
       <c r="AA2">
-        <v>-114.5131954407535</v>
+        <v>-114.5131954407487</v>
       </c>
       <c r="AB2">
-        <v>-114.5131954407667</v>
+        <v>-114.5131954407395</v>
       </c>
       <c r="AC2">
         <v>136.6657411464604</v>
@@ -4603,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8928555332546844</v>
+        <v>0.8928555332546843</v>
       </c>
       <c r="AH2">
         <v>0.9446106203901293</v>
@@ -4612,16 +4612,16 @@
         <v>1.014888974463672</v>
       </c>
       <c r="AJ2">
-        <v>0.6342405043354559</v>
+        <v>0.634240504335456</v>
       </c>
       <c r="AK2">
-        <v>0.9425752860361225</v>
+        <v>0.9425752860361223</v>
       </c>
       <c r="AL2">
         <v>1.180796373306989</v>
       </c>
       <c r="AM2">
-        <v>-7.128181818491637</v>
+        <v>-7.128181818491625</v>
       </c>
       <c r="AN2">
         <v>-118.9878906721926</v>
@@ -4630,13 +4630,13 @@
         <v>116.8120844345216</v>
       </c>
       <c r="AP2">
-        <v>1.665741161973187</v>
+        <v>1.665741161973235</v>
       </c>
       <c r="AQ2">
         <v>-130.1934967078016</v>
       </c>
       <c r="AR2">
-        <v>121.0088117719532</v>
+        <v>121.0088117719531</v>
       </c>
     </row>
   </sheetData>
@@ -4791,10 +4791,10 @@
         <v>1.035889633734118</v>
       </c>
       <c r="C2">
-        <v>0.0005551345763019315</v>
+        <v>0.0005551345763019103</v>
       </c>
       <c r="D2">
-        <v>0.0005551345763016516</v>
+        <v>0.0005551345763019823</v>
       </c>
       <c r="E2">
         <v>1.035710406082399</v>
@@ -4809,10 +4809,10 @@
         <v>11.96142317774272</v>
       </c>
       <c r="I2">
-        <v>0.006410141941287781</v>
+        <v>0.006410141941287535</v>
       </c>
       <c r="J2">
-        <v>0.006410141941284548</v>
+        <v>0.006410141941288367</v>
       </c>
       <c r="K2">
         <v>11.9593536350834</v>
@@ -4824,49 +4824,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>8.61432307590413</v>
+        <v>8.614323075904119</v>
       </c>
       <c r="O2">
-        <v>0.006036631569588754</v>
+        <v>0.006036631569588482</v>
       </c>
       <c r="P2">
-        <v>-0.004065327085942332</v>
+        <v>-0.004065327085947163</v>
       </c>
       <c r="Q2">
-        <v>-5.363480227314734</v>
+        <v>-5.363480227314723</v>
       </c>
       <c r="R2">
-        <v>-4.817115396587726E-11</v>
+        <v>-4.817393985560517E-11</v>
       </c>
       <c r="S2">
-        <v>-4.802057520624759E-09</v>
+        <v>-4.802052006224878E-09</v>
       </c>
       <c r="T2">
-        <v>6.312848364667321</v>
+        <v>6.312848364667334</v>
       </c>
       <c r="U2">
-        <v>-0.0004724106998723624</v>
+        <v>-0.0004724106998728516</v>
       </c>
       <c r="V2">
-        <v>-0.005078948493509238</v>
+        <v>-0.005078948493510333</v>
       </c>
       <c r="W2">
-        <v>-5.36348023021802</v>
+        <v>-5.363480230218032</v>
       </c>
       <c r="X2">
-        <v>-4.065631023489448E-09</v>
+        <v>-4.065630861704757E-09</v>
       </c>
       <c r="Y2">
-        <v>1.698281583200238E-09</v>
+        <v>1.69828326623497E-09</v>
       </c>
       <c r="Z2">
-        <v>-43.36332196693328</v>
+        <v>-43.36332196693336</v>
       </c>
       <c r="AA2">
-        <v>-114.5131954407535</v>
+        <v>-114.5131954407487</v>
       </c>
       <c r="AB2">
-        <v>-114.5131954407667</v>
+        <v>-114.5131954407395</v>
       </c>
       <c r="AC2">
         <v>136.6657411464604</v>
@@ -4878,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8928555332546844</v>
+        <v>0.8928555332546843</v>
       </c>
       <c r="AH2">
         <v>0.9446106203901293</v>
@@ -4887,16 +4887,16 @@
         <v>1.014888974463672</v>
       </c>
       <c r="AJ2">
-        <v>0.6342405043354559</v>
+        <v>0.634240504335456</v>
       </c>
       <c r="AK2">
-        <v>0.9425752860361225</v>
+        <v>0.9425752860361223</v>
       </c>
       <c r="AL2">
         <v>1.180796373306989</v>
       </c>
       <c r="AM2">
-        <v>-7.128181818491637</v>
+        <v>-7.128181818491625</v>
       </c>
       <c r="AN2">
         <v>-118.9878906721926</v>
@@ -4905,13 +4905,13 @@
         <v>116.8120844345216</v>
       </c>
       <c r="AP2">
-        <v>1.665741161973187</v>
+        <v>1.665741161973235</v>
       </c>
       <c r="AQ2">
         <v>-130.1934967078016</v>
       </c>
       <c r="AR2">
-        <v>121.0088117719532</v>
+        <v>121.0088117719531</v>
       </c>
     </row>
   </sheetData>
@@ -5066,73 +5066,73 @@
         <v>0.001143871084791532</v>
       </c>
       <c r="C2">
-        <v>5.026871232902589</v>
+        <v>5.026871232902588</v>
       </c>
       <c r="D2">
-        <v>2.97283270749978</v>
+        <v>2.972832707499777</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.026925725199458</v>
+        <v>5.026925725199459</v>
       </c>
       <c r="G2">
-        <v>2.971978874847184</v>
+        <v>2.971978874847185</v>
       </c>
       <c r="H2">
         <v>0.0132082855744524</v>
       </c>
       <c r="I2">
-        <v>58.04530918995791</v>
+        <v>58.0453091899579</v>
       </c>
       <c r="J2">
-        <v>34.32731527861444</v>
+        <v>34.32731527861441</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>58.04593841280324</v>
+        <v>58.04593841280325</v>
       </c>
       <c r="M2">
-        <v>34.31745606837805</v>
+        <v>34.31745606837807</v>
       </c>
       <c r="N2">
-        <v>-0.0002505500822160712</v>
+        <v>-0.0002505500822160666</v>
       </c>
       <c r="O2">
-        <v>31.94042916440145</v>
+        <v>31.94042916440144</v>
       </c>
       <c r="P2">
-        <v>-0.2508696004403674</v>
+        <v>-0.2508696004403959</v>
       </c>
       <c r="Q2">
-        <v>-9.750546482709596E-09</v>
+        <v>-9.750561312920687E-09</v>
       </c>
       <c r="R2">
-        <v>2.3549461200191E-10</v>
+        <v>2.354951058178877E-10</v>
       </c>
       <c r="S2">
-        <v>1.560489243074269E-10</v>
+        <v>1.56060038581487E-10</v>
       </c>
       <c r="T2">
         <v>-0.01290413886791865</v>
       </c>
       <c r="U2">
-        <v>7.953445881180603</v>
+        <v>7.953445881180619</v>
       </c>
       <c r="V2">
-        <v>16.03313910681056</v>
+        <v>16.03313910681054</v>
       </c>
       <c r="W2">
-        <v>-3.442933648091711E-09</v>
+        <v>-3.442943086878E-09</v>
       </c>
       <c r="X2">
-        <v>-1.520633510766607E-10</v>
+        <v>-1.52069776522664E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.239094838984857E-11</v>
+        <v>-5.239559964126709E-11</v>
       </c>
       <c r="Z2">
         <v>82.86821583345767</v>
@@ -5141,22 +5141,22 @@
         <v>175.5922528769733</v>
       </c>
       <c r="AB2">
-        <v>41.15861451898618</v>
+        <v>41.1586145189861</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-4.394724263667608</v>
+        <v>-4.394724263667635</v>
       </c>
       <c r="AE2">
-        <v>-138.8560581155531</v>
+        <v>-138.8560581155532</v>
       </c>
       <c r="AG2">
         <v>0.9771571744427107</v>
       </c>
       <c r="AH2">
-        <v>0.5670703897403274</v>
+        <v>0.5670703897403275</v>
       </c>
       <c r="AI2">
         <v>0.4671236747649692</v>
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-8.244114005996627</v>
+        <v>-8.244114005996606</v>
       </c>
       <c r="AN2">
         <v>-170.4249704778445</v>
@@ -5180,7 +5180,7 @@
         <v>132.055045115756</v>
       </c>
       <c r="AP2">
-        <v>-12.52501517682083</v>
+        <v>-12.52501517682081</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -5338,103 +5338,103 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001143871084790666</v>
+        <v>0.001143871084789649</v>
       </c>
       <c r="C2">
-        <v>5.026871232902587</v>
+        <v>5.026871232902589</v>
       </c>
       <c r="D2">
-        <v>2.972832707499776</v>
+        <v>2.972832707499778</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.026925725199458</v>
+        <v>5.026925725199464</v>
       </c>
       <c r="G2">
-        <v>2.971978874847183</v>
+        <v>2.971978874847184</v>
       </c>
       <c r="H2">
-        <v>0.01320828557444241</v>
+        <v>0.01320828557443066</v>
       </c>
       <c r="I2">
-        <v>58.04530918995789</v>
+        <v>58.04530918995791</v>
       </c>
       <c r="J2">
-        <v>34.3273152786144</v>
+        <v>34.32731527861441</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>58.04593841280324</v>
+        <v>58.04593841280332</v>
       </c>
       <c r="M2">
         <v>34.31745606837805</v>
       </c>
       <c r="N2">
-        <v>-0.00025055008221932</v>
+        <v>-0.000250550082236318</v>
       </c>
       <c r="O2">
-        <v>31.94042916440142</v>
+        <v>31.94042916440144</v>
       </c>
       <c r="P2">
-        <v>-0.2508696004404196</v>
+        <v>-0.2508696004404089</v>
       </c>
       <c r="Q2">
-        <v>-9.750576143131773E-09</v>
+        <v>-9.750554569846803E-09</v>
       </c>
       <c r="R2">
-        <v>2.355000498159583E-10</v>
+        <v>2.355237763360619E-10</v>
       </c>
       <c r="S2">
-        <v>1.560751090753566E-10</v>
+        <v>1.560604009357314E-10</v>
       </c>
       <c r="T2">
-        <v>-0.01290413886790882</v>
+        <v>-0.01290413886789701</v>
       </c>
       <c r="U2">
-        <v>7.953445881180611</v>
+        <v>7.953445881180595</v>
       </c>
       <c r="V2">
         <v>16.03313910681054</v>
       </c>
       <c r="W2">
-        <v>-3.442952525664286E-09</v>
+        <v>-3.442970051587781E-09</v>
       </c>
       <c r="X2">
-        <v>-1.520500063686761E-10</v>
+        <v>-1.520223293207524E-10</v>
       </c>
       <c r="Y2">
-        <v>-5.241888557524008E-11</v>
+        <v>-5.24009756011747E-11</v>
       </c>
       <c r="Z2">
-        <v>82.86821583347296</v>
+        <v>82.8682158335494</v>
       </c>
       <c r="AA2">
         <v>175.5922528769733</v>
       </c>
       <c r="AB2">
-        <v>41.15861451898606</v>
+        <v>41.15861451898609</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-4.394724263667636</v>
+        <v>-4.394724263667622</v>
       </c>
       <c r="AE2">
         <v>-138.8560581155532</v>
       </c>
       <c r="AG2">
-        <v>0.9771571744427107</v>
+        <v>0.9771571744427108</v>
       </c>
       <c r="AH2">
-        <v>0.5670703897403271</v>
+        <v>0.5670703897403272</v>
       </c>
       <c r="AI2">
-        <v>0.4671236747649694</v>
+        <v>0.4671236747649692</v>
       </c>
       <c r="AJ2">
         <v>1.312059302960688</v>
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-8.244114005996606</v>
+        <v>-8.244114005996614</v>
       </c>
       <c r="AN2">
         <v>-170.4249704778445</v>
@@ -5613,10 +5613,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.000378989326656751</v>
+        <v>0.0003789893266567694</v>
       </c>
       <c r="C2">
-        <v>1.382386873692202</v>
+        <v>1.382386873692204</v>
       </c>
       <c r="D2">
         <v>1.177072767658897</v>
@@ -5625,16 +5625,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.382520063691103</v>
+        <v>1.382520063691104</v>
       </c>
       <c r="G2">
-        <v>1.17670513860627</v>
+        <v>1.176705138606269</v>
       </c>
       <c r="H2">
-        <v>0.004376191795305405</v>
+        <v>0.004376191795305617</v>
       </c>
       <c r="I2">
-        <v>15.96242867300797</v>
+        <v>15.96242867300798</v>
       </c>
       <c r="J2">
         <v>13.59166558527284</v>
@@ -5643,22 +5643,22 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15.96396661864234</v>
+        <v>15.96396661864235</v>
       </c>
       <c r="M2">
         <v>13.58742057062291</v>
       </c>
       <c r="N2">
-        <v>0.0006412014006246014</v>
+        <v>0.0006412014006258492</v>
       </c>
       <c r="O2">
         <v>11.98351855411372</v>
       </c>
       <c r="P2">
-        <v>7.741742056905995</v>
+        <v>7.741742056905996</v>
       </c>
       <c r="Q2">
-        <v>-2.609763671324719E-09</v>
+        <v>-2.60976823479766E-09</v>
       </c>
       <c r="R2">
         <v>-9.556808632932945</v>
@@ -5667,25 +5667,25 @@
         <v>-6.923174913730128</v>
       </c>
       <c r="T2">
-        <v>-0.004569102167846475</v>
+        <v>-0.004569102167846529</v>
       </c>
       <c r="U2">
-        <v>9.557683331464952</v>
+        <v>9.55768333146497</v>
       </c>
       <c r="V2">
         <v>9.294480388845987</v>
       </c>
       <c r="W2">
-        <v>-1.530290013101739E-09</v>
+        <v>-1.530295135431716E-09</v>
       </c>
       <c r="X2">
-        <v>-9.556808635331512</v>
+        <v>-9.556808635331528</v>
       </c>
       <c r="Y2">
         <v>-6.923174919701175</v>
       </c>
       <c r="Z2">
-        <v>79.62743609723184</v>
+        <v>79.62743609721657</v>
       </c>
       <c r="AA2">
         <v>-169.8047984139787</v>
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.20990687633839</v>
+        <v>10.20990687633835</v>
       </c>
       <c r="AE2">
         <v>-114.438849573896</v>
@@ -5709,7 +5709,7 @@
         <v>0.96026804586595</v>
       </c>
       <c r="AI2">
-        <v>0.8899836711803116</v>
+        <v>0.8899836711803119</v>
       </c>
       <c r="AJ2">
         <v>1.158599621240366</v>
@@ -5718,10 +5718,10 @@
         <v>0.8466171789416779</v>
       </c>
       <c r="AL2">
-        <v>0.7205817918869083</v>
+        <v>0.7205817918869086</v>
       </c>
       <c r="AM2">
-        <v>-2.384172943571885</v>
+        <v>-2.384172943571882</v>
       </c>
       <c r="AN2">
         <v>-131.2300202118273</v>
@@ -5730,7 +5730,7 @@
         <v>115.7733745763009</v>
       </c>
       <c r="AP2">
-        <v>-4.827878725560209</v>
+        <v>-4.827878725560208</v>
       </c>
       <c r="AQ2">
         <v>-124.7900931164661</v>
@@ -5888,112 +5888,112 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003789893266568433</v>
+        <v>0.0003789893266557975</v>
       </c>
       <c r="C2">
-        <v>1.382386873692204</v>
+        <v>1.382386873692202</v>
       </c>
       <c r="D2">
-        <v>1.177072767658896</v>
+        <v>1.177072767658897</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.382520063691104</v>
+        <v>1.382520063691103</v>
       </c>
       <c r="G2">
         <v>1.176705138606268</v>
       </c>
       <c r="H2">
-        <v>0.00437619179530647</v>
+        <v>0.004376191795294394</v>
       </c>
       <c r="I2">
-        <v>15.96242867300798</v>
+        <v>15.96242867300796</v>
       </c>
       <c r="J2">
-        <v>13.59166558527283</v>
+        <v>13.59166558527284</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15.96396661864235</v>
+        <v>15.96396661864233</v>
       </c>
       <c r="M2">
-        <v>13.5874205706229</v>
+        <v>13.58742057062289</v>
       </c>
       <c r="N2">
-        <v>0.000641201400630839</v>
+        <v>0.0006412014006288635</v>
       </c>
       <c r="O2">
         <v>11.98351855411371</v>
       </c>
       <c r="P2">
-        <v>7.741742056905975</v>
+        <v>7.74174205690601</v>
       </c>
       <c r="Q2">
-        <v>-2.609769371035063E-09</v>
+        <v>-2.60976823479766E-09</v>
       </c>
       <c r="R2">
-        <v>-9.556808632932944</v>
+        <v>-9.556808632932942</v>
       </c>
       <c r="S2">
-        <v>-6.923174913730112</v>
+        <v>-6.92317491373013</v>
       </c>
       <c r="T2">
-        <v>-0.004569102167846735</v>
+        <v>-0.004569102167834157</v>
       </c>
       <c r="U2">
-        <v>9.557683331464968</v>
+        <v>9.557683331464958</v>
       </c>
       <c r="V2">
-        <v>9.294480388845985</v>
+        <v>9.294480388845971</v>
       </c>
       <c r="W2">
-        <v>-1.530292285576544E-09</v>
+        <v>-1.530295135431716E-09</v>
       </c>
       <c r="X2">
-        <v>-9.556808635331521</v>
+        <v>-9.556808635331514</v>
       </c>
       <c r="Y2">
-        <v>-6.92317491970118</v>
+        <v>-6.923174919701161</v>
       </c>
       <c r="Z2">
-        <v>79.62743609715558</v>
+        <v>79.62743609715817</v>
       </c>
       <c r="AA2">
         <v>-169.8047984139787</v>
       </c>
       <c r="AB2">
-        <v>65.56563408676568</v>
+        <v>65.56563408676584</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.20990687633837</v>
+        <v>10.20990687633838</v>
       </c>
       <c r="AE2">
-        <v>-114.4388495738961</v>
+        <v>-114.4388495738959</v>
       </c>
       <c r="AG2">
         <v>1.054312579845774</v>
       </c>
       <c r="AH2">
-        <v>0.9602680458659498</v>
+        <v>0.9602680458659503</v>
       </c>
       <c r="AI2">
-        <v>0.8899836711803117</v>
+        <v>0.889983671180312</v>
       </c>
       <c r="AJ2">
         <v>1.158599621240366</v>
       </c>
       <c r="AK2">
-        <v>0.8466171789416777</v>
+        <v>0.8466171789416781</v>
       </c>
       <c r="AL2">
-        <v>0.7205817918869085</v>
+        <v>0.7205817918869087</v>
       </c>
       <c r="AM2">
         <v>-2.384172943571881</v>
@@ -6005,7 +6005,7 @@
         <v>115.7733745763009</v>
       </c>
       <c r="AP2">
-        <v>-4.827878725560207</v>
+        <v>-4.8278787255602</v>
       </c>
       <c r="AQ2">
         <v>-124.7900931164661</v>
@@ -6163,79 +6163,79 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001105760050856239</v>
+        <v>0.001105760050858358</v>
       </c>
       <c r="C2">
-        <v>3.92133157943606</v>
+        <v>3.921331579436062</v>
       </c>
       <c r="D2">
-        <v>2.491992615620697</v>
+        <v>2.491992615620696</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.92161925581113</v>
+        <v>3.921619255811131</v>
       </c>
       <c r="G2">
-        <v>2.491243992186032</v>
+        <v>2.491243992186033</v>
       </c>
       <c r="H2">
-        <v>0.01276821726041968</v>
+        <v>0.01276821726044415</v>
       </c>
       <c r="I2">
-        <v>45.2796368593838</v>
+        <v>45.27963685938381</v>
       </c>
       <c r="J2">
-        <v>28.77505214894338</v>
+        <v>28.77505214894337</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45.28295866003551</v>
+        <v>45.28295866003553</v>
       </c>
       <c r="M2">
-        <v>28.76640779011287</v>
+        <v>28.76640779011288</v>
       </c>
       <c r="N2">
-        <v>-0.0001657433366718191</v>
+        <v>-0.0001657433366652823</v>
       </c>
       <c r="O2">
-        <v>30.31563093809499</v>
+        <v>30.31563093809501</v>
       </c>
       <c r="P2">
-        <v>-0.1080137594025518</v>
+        <v>-0.1080137594025482</v>
       </c>
       <c r="Q2">
-        <v>-1.107386424272076E-08</v>
+        <v>-1.107387479245534E-08</v>
       </c>
       <c r="R2">
-        <v>-1.701457724143477E-10</v>
+        <v>-1.701333834150182E-10</v>
       </c>
       <c r="S2">
-        <v>-2.613538182463858E-11</v>
+        <v>-2.613787785606156E-11</v>
       </c>
       <c r="T2">
-        <v>-0.01215427121313571</v>
+        <v>-0.0121542712131591</v>
       </c>
       <c r="U2">
-        <v>1.849625463043424</v>
+        <v>1.849625463043407</v>
       </c>
       <c r="V2">
         <v>12.13153436196901</v>
       </c>
       <c r="W2">
-        <v>-2.245517936965018E-09</v>
+        <v>-2.24548475026218E-09</v>
       </c>
       <c r="X2">
-        <v>-1.936979700434276E-10</v>
+        <v>-1.937000868901251E-10</v>
       </c>
       <c r="Y2">
-        <v>-1.618401753554499E-10</v>
+        <v>-1.618302598224982E-10</v>
       </c>
       <c r="Z2">
-        <v>84.60871947160607</v>
+        <v>84.60871947157372</v>
       </c>
       <c r="AA2">
         <v>-170.3193910162658</v>
@@ -6247,22 +6247,22 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.69620866270755</v>
+        <v>9.696208662707559</v>
       </c>
       <c r="AE2">
         <v>-142.7892737871882</v>
       </c>
       <c r="AG2">
-        <v>0.9520045753620056</v>
+        <v>0.9520045753620062</v>
       </c>
       <c r="AH2">
-        <v>0.6707651729559315</v>
+        <v>0.6707651729559316</v>
       </c>
       <c r="AI2">
-        <v>0.4216157504340798</v>
+        <v>0.42161575043408</v>
       </c>
       <c r="AJ2">
-        <v>1.315056832745734</v>
+        <v>1.315056832745735</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6271,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-6.172553624091364</v>
+        <v>-6.17255362409139</v>
       </c>
       <c r="AN2">
         <v>-166.827973412876</v>
@@ -6280,7 +6280,7 @@
         <v>127.7395623824123</v>
       </c>
       <c r="AP2">
-        <v>-8.930089734159836</v>
+        <v>-8.93008973415988</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -6357,10 +6357,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.309686024628782</v>
+        <v>1.309686024628783</v>
       </c>
       <c r="C2">
-        <v>1.309686024628782</v>
+        <v>1.309686024628783</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6369,10 +6369,10 @@
         <v>2.837059479583174</v>
       </c>
       <c r="F2">
-        <v>45.3688547323991</v>
+        <v>45.36885473239911</v>
       </c>
       <c r="G2">
-        <v>45.3688547323991</v>
+        <v>45.36885473239911</v>
       </c>
       <c r="H2">
         <v>28.40499517047036</v>
@@ -6381,13 +6381,13 @@
         <v>-25.72916224161305</v>
       </c>
       <c r="J2">
-        <v>28.76520341755289</v>
+        <v>28.76520341755291</v>
       </c>
       <c r="K2">
-        <v>-25.72916225404872</v>
+        <v>-25.72916225404873</v>
       </c>
       <c r="L2">
-        <v>-54.52967391402492</v>
+        <v>-54.52967391402493</v>
       </c>
       <c r="M2">
         <v>125.4703260859678</v>
@@ -6396,13 +6396,13 @@
         <v>0.8910570420386134</v>
       </c>
       <c r="O2">
-        <v>0.8020156209364414</v>
+        <v>0.8020156209364413</v>
       </c>
       <c r="P2">
-        <v>-9.168679204911154</v>
+        <v>-9.168679204911147</v>
       </c>
       <c r="Q2">
-        <v>-9.529673900180361</v>
+        <v>-9.529673900180356</v>
       </c>
     </row>
   </sheetData>
@@ -6554,79 +6554,79 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001105760050856239</v>
+        <v>0.001105760050858358</v>
       </c>
       <c r="C2">
-        <v>3.92133157943606</v>
+        <v>3.921331579436062</v>
       </c>
       <c r="D2">
-        <v>2.491992615620697</v>
+        <v>2.491992615620696</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.92161925581113</v>
+        <v>3.921619255811131</v>
       </c>
       <c r="G2">
-        <v>2.491243992186032</v>
+        <v>2.491243992186033</v>
       </c>
       <c r="H2">
-        <v>0.01276821726041968</v>
+        <v>0.01276821726044415</v>
       </c>
       <c r="I2">
-        <v>45.2796368593838</v>
+        <v>45.27963685938381</v>
       </c>
       <c r="J2">
-        <v>28.77505214894338</v>
+        <v>28.77505214894337</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45.28295866003551</v>
+        <v>45.28295866003553</v>
       </c>
       <c r="M2">
-        <v>28.76640779011287</v>
+        <v>28.76640779011288</v>
       </c>
       <c r="N2">
-        <v>-0.0001657433366718191</v>
+        <v>-0.0001657433366652823</v>
       </c>
       <c r="O2">
-        <v>30.31563093809499</v>
+        <v>30.31563093809501</v>
       </c>
       <c r="P2">
-        <v>-0.1080137594025518</v>
+        <v>-0.1080137594025482</v>
       </c>
       <c r="Q2">
-        <v>-1.107386424272076E-08</v>
+        <v>-1.107387479245534E-08</v>
       </c>
       <c r="R2">
-        <v>-1.701457724143477E-10</v>
+        <v>-1.701333834150182E-10</v>
       </c>
       <c r="S2">
-        <v>-2.613538182463858E-11</v>
+        <v>-2.613787785606156E-11</v>
       </c>
       <c r="T2">
-        <v>-0.01215427121313571</v>
+        <v>-0.0121542712131591</v>
       </c>
       <c r="U2">
-        <v>1.849625463043424</v>
+        <v>1.849625463043407</v>
       </c>
       <c r="V2">
         <v>12.13153436196901</v>
       </c>
       <c r="W2">
-        <v>-2.245517936965018E-09</v>
+        <v>-2.24548475026218E-09</v>
       </c>
       <c r="X2">
-        <v>-1.936979700434276E-10</v>
+        <v>-1.937000868901251E-10</v>
       </c>
       <c r="Y2">
-        <v>-1.618401753554499E-10</v>
+        <v>-1.618302598224982E-10</v>
       </c>
       <c r="Z2">
-        <v>84.60871947160607</v>
+        <v>84.60871947157372</v>
       </c>
       <c r="AA2">
         <v>-170.3193910162658</v>
@@ -6638,22 +6638,22 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.69620866270755</v>
+        <v>9.696208662707559</v>
       </c>
       <c r="AE2">
         <v>-142.7892737871882</v>
       </c>
       <c r="AG2">
-        <v>0.9520045753620056</v>
+        <v>0.9520045753620062</v>
       </c>
       <c r="AH2">
-        <v>0.6707651729559315</v>
+        <v>0.6707651729559316</v>
       </c>
       <c r="AI2">
-        <v>0.4216157504340798</v>
+        <v>0.42161575043408</v>
       </c>
       <c r="AJ2">
-        <v>1.315056832745734</v>
+        <v>1.315056832745735</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-6.172553624091364</v>
+        <v>-6.17255362409139</v>
       </c>
       <c r="AN2">
         <v>-166.827973412876</v>
@@ -6671,7 +6671,7 @@
         <v>127.7395623824123</v>
       </c>
       <c r="AP2">
-        <v>-8.930089734159836</v>
+        <v>-8.93008973415988</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004965920471321641</v>
+        <v>0.0004965920471329187</v>
       </c>
       <c r="C2">
-        <v>1.210481473029655</v>
+        <v>1.210481473029656</v>
       </c>
       <c r="D2">
-        <v>0.9669780959040256</v>
+        <v>0.9669780959040252</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6844,16 +6844,16 @@
         <v>1.210751047298469</v>
       </c>
       <c r="G2">
-        <v>0.9664867209022838</v>
+        <v>0.9664867209022846</v>
       </c>
       <c r="H2">
-        <v>0.005734151041783646</v>
+        <v>0.005734151041792359</v>
       </c>
       <c r="I2">
-        <v>13.97743608605452</v>
+        <v>13.97743608605453</v>
       </c>
       <c r="J2">
-        <v>11.16570127941322</v>
+        <v>11.16570127941321</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -6862,49 +6862,49 @@
         <v>13.98054886158785</v>
       </c>
       <c r="M2">
-        <v>11.16002736962264</v>
+        <v>11.16002736962266</v>
       </c>
       <c r="N2">
-        <v>0.001401851070263689</v>
+        <v>0.001401851070262163</v>
       </c>
       <c r="O2">
         <v>10.45747396702612</v>
       </c>
       <c r="P2">
-        <v>5.683293932532261</v>
+        <v>5.683293932532258</v>
       </c>
       <c r="Q2">
-        <v>-3.881190881459014E-09</v>
+        <v>-3.881189009759431E-09</v>
       </c>
       <c r="R2">
-        <v>-7.329590494418022</v>
+        <v>-7.329590494418018</v>
       </c>
       <c r="S2">
-        <v>-4.67048290627889</v>
+        <v>-4.670482906278894</v>
       </c>
       <c r="T2">
-        <v>-0.005370939161857956</v>
+        <v>-0.005370939161867071</v>
       </c>
       <c r="U2">
-        <v>6.607602901287278</v>
+        <v>6.607602901287282</v>
       </c>
       <c r="V2">
-        <v>7.06265571418042</v>
+        <v>7.062655714180416</v>
       </c>
       <c r="W2">
-        <v>-1.894373546474882E-09</v>
+        <v>-1.894368412050891E-09</v>
       </c>
       <c r="X2">
-        <v>-7.329590495048787</v>
+        <v>-7.329590495048789</v>
       </c>
       <c r="Y2">
         <v>-4.670482911810214</v>
       </c>
       <c r="Z2">
-        <v>72.99235436184145</v>
+        <v>72.99235436188046</v>
       </c>
       <c r="AA2">
-        <v>-164.1397217055246</v>
+        <v>-164.1397217055247</v>
       </c>
       <c r="AB2">
         <v>64.6819630293035</v>
@@ -6913,16 +6913,16 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>15.88001650166773</v>
+        <v>15.88001650166772</v>
       </c>
       <c r="AE2">
         <v>-115.3222920094987</v>
       </c>
       <c r="AG2">
-        <v>0.9680371887624606</v>
+        <v>0.9680371887624607</v>
       </c>
       <c r="AH2">
-        <v>0.8850043739021403</v>
+        <v>0.8850043739021402</v>
       </c>
       <c r="AI2">
         <v>0.8118943814477215</v>
@@ -6934,10 +6934,10 @@
         <v>0.741430568063951</v>
       </c>
       <c r="AL2">
-        <v>0.5918498274279671</v>
+        <v>0.5918498274279669</v>
       </c>
       <c r="AM2">
-        <v>-2.379415652546996</v>
+        <v>-2.379415652547003</v>
       </c>
       <c r="AN2">
         <v>-131.8527891286921</v>
@@ -6946,7 +6946,7 @@
         <v>115.858453197156</v>
       </c>
       <c r="AP2">
-        <v>-5.992544797940907</v>
+        <v>-5.992544797940928</v>
       </c>
       <c r="AQ2">
         <v>-119.1199834958614</v>
@@ -7104,13 +7104,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004965920471321641</v>
+        <v>0.0004965920471329187</v>
       </c>
       <c r="C2">
-        <v>1.210481473029655</v>
+        <v>1.210481473029656</v>
       </c>
       <c r="D2">
-        <v>0.9669780959040256</v>
+        <v>0.9669780959040252</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7119,16 +7119,16 @@
         <v>1.210751047298469</v>
       </c>
       <c r="G2">
-        <v>0.9664867209022838</v>
+        <v>0.9664867209022846</v>
       </c>
       <c r="H2">
-        <v>0.005734151041783646</v>
+        <v>0.005734151041792359</v>
       </c>
       <c r="I2">
-        <v>13.97743608605452</v>
+        <v>13.97743608605453</v>
       </c>
       <c r="J2">
-        <v>11.16570127941322</v>
+        <v>11.16570127941321</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -7137,49 +7137,49 @@
         <v>13.98054886158785</v>
       </c>
       <c r="M2">
-        <v>11.16002736962264</v>
+        <v>11.16002736962266</v>
       </c>
       <c r="N2">
-        <v>0.001401851070263689</v>
+        <v>0.001401851070262163</v>
       </c>
       <c r="O2">
         <v>10.45747396702612</v>
       </c>
       <c r="P2">
-        <v>5.683293932532261</v>
+        <v>5.683293932532258</v>
       </c>
       <c r="Q2">
-        <v>-3.881190881459014E-09</v>
+        <v>-3.881189009759431E-09</v>
       </c>
       <c r="R2">
-        <v>-7.329590494418022</v>
+        <v>-7.329590494418018</v>
       </c>
       <c r="S2">
-        <v>-4.67048290627889</v>
+        <v>-4.670482906278894</v>
       </c>
       <c r="T2">
-        <v>-0.005370939161857956</v>
+        <v>-0.005370939161867071</v>
       </c>
       <c r="U2">
-        <v>6.607602901287278</v>
+        <v>6.607602901287282</v>
       </c>
       <c r="V2">
-        <v>7.06265571418042</v>
+        <v>7.062655714180416</v>
       </c>
       <c r="W2">
-        <v>-1.894373546474882E-09</v>
+        <v>-1.894368412050891E-09</v>
       </c>
       <c r="X2">
-        <v>-7.329590495048787</v>
+        <v>-7.329590495048789</v>
       </c>
       <c r="Y2">
         <v>-4.670482911810214</v>
       </c>
       <c r="Z2">
-        <v>72.99235436184145</v>
+        <v>72.99235436188046</v>
       </c>
       <c r="AA2">
-        <v>-164.1397217055246</v>
+        <v>-164.1397217055247</v>
       </c>
       <c r="AB2">
         <v>64.6819630293035</v>
@@ -7188,16 +7188,16 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>15.88001650166773</v>
+        <v>15.88001650166772</v>
       </c>
       <c r="AE2">
         <v>-115.3222920094987</v>
       </c>
       <c r="AG2">
-        <v>0.9680371887624606</v>
+        <v>0.9680371887624607</v>
       </c>
       <c r="AH2">
-        <v>0.8850043739021403</v>
+        <v>0.8850043739021402</v>
       </c>
       <c r="AI2">
         <v>0.8118943814477215</v>
@@ -7209,10 +7209,10 @@
         <v>0.741430568063951</v>
       </c>
       <c r="AL2">
-        <v>0.5918498274279671</v>
+        <v>0.5918498274279669</v>
       </c>
       <c r="AM2">
-        <v>-2.379415652546996</v>
+        <v>-2.379415652547003</v>
       </c>
       <c r="AN2">
         <v>-131.8527891286921</v>
@@ -7221,7 +7221,7 @@
         <v>115.858453197156</v>
       </c>
       <c r="AP2">
-        <v>-5.992544797940907</v>
+        <v>-5.992544797940928</v>
       </c>
       <c r="AQ2">
         <v>-119.1199834958614</v>
@@ -7298,52 +7298,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.309686024628784</v>
+        <v>1.309686024628783</v>
       </c>
       <c r="C2">
-        <v>1.309686024628784</v>
+        <v>1.309686024628783</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.837059479583177</v>
+        <v>2.837059479583175</v>
       </c>
       <c r="F2">
-        <v>45.36885473239915</v>
+        <v>45.36885473239911</v>
       </c>
       <c r="G2">
-        <v>45.36885473239915</v>
+        <v>45.36885473239911</v>
       </c>
       <c r="H2">
-        <v>28.40499517047039</v>
+        <v>28.40499517047034</v>
       </c>
       <c r="I2">
-        <v>-25.72916224161307</v>
+        <v>-25.72916224161303</v>
       </c>
       <c r="J2">
-        <v>28.76520341755291</v>
+        <v>28.76520341755294</v>
       </c>
       <c r="K2">
-        <v>-25.72916225404874</v>
+        <v>-25.72916225404877</v>
       </c>
       <c r="L2">
-        <v>-54.52967391402493</v>
+        <v>-54.52967391402498</v>
       </c>
       <c r="M2">
-        <v>125.4703260859678</v>
+        <v>125.4703260859677</v>
       </c>
       <c r="N2">
-        <v>0.891057042038613</v>
+        <v>0.8910570420386137</v>
       </c>
       <c r="O2">
-        <v>0.8020156209364409</v>
+        <v>0.8020156209364414</v>
       </c>
       <c r="P2">
-        <v>-9.168679204911165</v>
+        <v>-9.16867920491114</v>
       </c>
       <c r="Q2">
-        <v>-9.529673900180375</v>
+        <v>-9.52967390018034</v>
       </c>
     </row>
   </sheetData>
@@ -7414,49 +7414,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.601610081638496</v>
+        <v>3.601610081638499</v>
       </c>
       <c r="C2">
-        <v>3.601610081638496</v>
+        <v>3.601610081638499</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.838062054648191</v>
+        <v>6.838062054648196</v>
       </c>
       <c r="F2">
-        <v>124.7634330090033</v>
+        <v>124.7634330090034</v>
       </c>
       <c r="G2">
-        <v>124.7634330090033</v>
+        <v>124.7634330090034</v>
       </c>
       <c r="H2">
-        <v>38.85252268584038</v>
+        <v>38.85252268584023</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>22.95972360762202</v>
+        <v>22.95972360762209</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-69.67231644738069</v>
+        <v>-69.67231644738079</v>
       </c>
       <c r="M2">
-        <v>110.327683552612</v>
+        <v>110.3276835526119</v>
       </c>
       <c r="N2">
-        <v>0.361720183501133</v>
+        <v>0.3617201835011319</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-39.09154322526819</v>
+        <v>-39.09154322526811</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -7530,49 +7530,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.601610081638496</v>
+        <v>3.601610081638499</v>
       </c>
       <c r="C2">
-        <v>3.601610081638496</v>
+        <v>3.601610081638499</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.838062054648191</v>
+        <v>6.838062054648196</v>
       </c>
       <c r="F2">
-        <v>124.7634330090033</v>
+        <v>124.7634330090034</v>
       </c>
       <c r="G2">
-        <v>124.7634330090033</v>
+        <v>124.7634330090034</v>
       </c>
       <c r="H2">
-        <v>38.85252268584038</v>
+        <v>38.85252268584023</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>22.95972360762202</v>
+        <v>22.95972360762209</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-69.67231644738069</v>
+        <v>-69.67231644738079</v>
       </c>
       <c r="M2">
-        <v>110.327683552612</v>
+        <v>110.3276835526119</v>
       </c>
       <c r="N2">
-        <v>0.361720183501133</v>
+        <v>0.3617201835011319</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-39.09154322526819</v>
+        <v>-39.09154322526811</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -7646,52 +7646,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.146247392614549</v>
+        <v>1.146247392614548</v>
       </c>
       <c r="C2">
-        <v>1.146247392614549</v>
+        <v>1.146247392614548</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.176279670202844</v>
+        <v>2.176279670202842</v>
       </c>
       <c r="F2">
-        <v>39.707174441035</v>
+        <v>39.70717444103497</v>
       </c>
       <c r="G2">
-        <v>39.707174441035</v>
+        <v>39.70717444103497</v>
       </c>
       <c r="H2">
-        <v>23.64358897071039</v>
+        <v>23.64358897071033</v>
       </c>
       <c r="I2">
-        <v>-19.70824627309619</v>
+        <v>-19.70824627309613</v>
       </c>
       <c r="J2">
-        <v>22.03381935746361</v>
+        <v>22.03381935746363</v>
       </c>
       <c r="K2">
-        <v>-19.70824628278309</v>
+        <v>-19.70824628278311</v>
       </c>
       <c r="L2">
-        <v>-52.63434508457832</v>
+        <v>-52.63434508457839</v>
       </c>
       <c r="M2">
-        <v>127.3656549154144</v>
+        <v>127.3656549154143</v>
       </c>
       <c r="N2">
-        <v>0.8139299031165274</v>
+        <v>0.8139299031165275</v>
       </c>
       <c r="O2">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="P2">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430418</v>
       </c>
       <c r="Q2">
-        <v>-7.634345070499267</v>
+        <v>-7.634345070499235</v>
       </c>
     </row>
   </sheetData>
@@ -7762,52 +7762,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.146247392614549</v>
+        <v>1.146247392614548</v>
       </c>
       <c r="C2">
-        <v>1.146247392614549</v>
+        <v>1.146247392614548</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.176279670202844</v>
+        <v>2.176279670202842</v>
       </c>
       <c r="F2">
-        <v>39.707174441035</v>
+        <v>39.70717444103497</v>
       </c>
       <c r="G2">
-        <v>39.707174441035</v>
+        <v>39.70717444103497</v>
       </c>
       <c r="H2">
-        <v>23.64358897071039</v>
+        <v>23.64358897071033</v>
       </c>
       <c r="I2">
-        <v>-19.70824627309619</v>
+        <v>-19.70824627309613</v>
       </c>
       <c r="J2">
-        <v>22.03381935746361</v>
+        <v>22.03381935746363</v>
       </c>
       <c r="K2">
-        <v>-19.70824628278309</v>
+        <v>-19.70824628278311</v>
       </c>
       <c r="L2">
-        <v>-52.63434508457832</v>
+        <v>-52.63434508457839</v>
       </c>
       <c r="M2">
-        <v>127.3656549154144</v>
+        <v>127.3656549154143</v>
       </c>
       <c r="N2">
-        <v>0.8139299031165274</v>
+        <v>0.8139299031165275</v>
       </c>
       <c r="O2">
-        <v>0.7019303077896066</v>
+        <v>0.7019303077896069</v>
       </c>
       <c r="P2">
-        <v>-9.652735617430441</v>
+        <v>-9.652735617430418</v>
       </c>
       <c r="Q2">
-        <v>-7.634345070499267</v>
+        <v>-7.634345070499235</v>
       </c>
     </row>
   </sheetData>
@@ -7959,73 +7959,73 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.70915442374498</v>
+        <v>3.709154423744984</v>
       </c>
       <c r="D2">
+        <v>3.709154423744979</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>3.709154423744982</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>3.709154423744977</v>
-      </c>
       <c r="G2">
-        <v>3.709154423744978</v>
+        <v>3.709154423744979</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42.82962610030111</v>
+        <v>42.82962610030116</v>
       </c>
       <c r="J2">
-        <v>42.82962610030113</v>
+        <v>42.8296261003011</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>42.82962610030107</v>
+        <v>42.82962610030114</v>
       </c>
       <c r="M2">
-        <v>42.82962610030109</v>
+        <v>42.8296261003011</v>
       </c>
       <c r="N2">
-        <v>-1.042129368361851E-14</v>
+        <v>-2.605323420904633E-14</v>
       </c>
       <c r="O2">
-        <v>30.17661447772221</v>
+        <v>30.17661447772224</v>
       </c>
       <c r="P2">
-        <v>-15.86847458187513</v>
+        <v>-15.86847458187512</v>
       </c>
       <c r="Q2">
-        <v>-5.210646841809377E-15</v>
+        <v>2.084258736723706E-14</v>
       </c>
       <c r="R2">
         <v>-23.02254452973952</v>
       </c>
       <c r="S2">
-        <v>23.02254452985794</v>
+        <v>23.02254452985792</v>
       </c>
       <c r="T2">
-        <v>-5.210646841809379E-15</v>
+        <v>-5.210646841809532E-15</v>
       </c>
       <c r="U2">
-        <v>3.130989834187371</v>
+        <v>3.130989834187394</v>
       </c>
       <c r="V2">
-        <v>13.10324558045219</v>
+        <v>13.10324558045218</v>
       </c>
       <c r="W2">
-        <v>1.042129368361851E-14</v>
+        <v>5.210646841809486E-15</v>
       </c>
       <c r="X2">
-        <v>4.986127873134736</v>
+        <v>4.986127873134732</v>
       </c>
       <c r="Y2">
-        <v>-4.986127873130089</v>
+        <v>-4.986127873130088</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -8034,13 +8034,13 @@
         <v>-167.7798457937528</v>
       </c>
       <c r="AB2">
-        <v>12.22015420623994</v>
+        <v>12.22015420623996</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>12.22015420623994</v>
+        <v>12.22015420623991</v>
       </c>
       <c r="AE2">
         <v>-167.7798457937528</v>
@@ -8049,7 +8049,7 @@
         <v>1.10000002383429</v>
       </c>
       <c r="AG2">
-        <v>0.708355667475826</v>
+        <v>0.7083556674758258</v>
       </c>
       <c r="AH2">
         <v>0.4804898682203931</v>
@@ -8058,13 +8058,13 @@
         <v>1.10000002383429</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119158046</v>
+        <v>0.5500000119158036</v>
       </c>
       <c r="AK2">
-        <v>0.5500000119184836</v>
+        <v>0.550000011918483</v>
       </c>
       <c r="AL2">
-        <v>5.537259256280933E-13</v>
+        <v>5.609847243447088E-13</v>
       </c>
       <c r="AM2">
         <v>-161.8562887546276</v>
@@ -8073,10 +8073,10 @@
         <v>152.6722796269628</v>
       </c>
       <c r="AO2">
-        <v>5.492245652284783E-13</v>
+        <v>5.691531544918663E-13</v>
       </c>
       <c r="AP2">
-        <v>179.9999999999541</v>
+        <v>179.999999999954</v>
       </c>
       <c r="AQ2">
         <v>-179.9999999999593</v>
